--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112774058</v>
+        <v>112774098</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtjärnen (Högtjärnen), Jmt</t>
+          <t>Högtjärnen, Högtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>489427</v>
       </c>
       <c r="R2" t="n">
-        <v>6945514</v>
+        <v>6945513</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -766,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Wännström </t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Wännström </t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112774098</v>
+        <v>112774058</v>
       </c>
       <c r="B3" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,35 +784,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtjärnen (Högtjärnen), Jmt</t>
+          <t>Högtjärnen, Högtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>489427</v>
       </c>
       <c r="R3" t="n">
-        <v>6945514</v>
+        <v>6945513</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -869,12 +859,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Wännström </t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Wännström </t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112774098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,8 +878,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112774058</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,6 +881,127 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112774058</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136171550</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högtjärn, Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489213</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6945585</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136171550</t>
         </is>
       </c>
     </row>
@@ -888,6 +1009,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
